--- a/data/BOLL/EXCLE/POET_1_20260826.xlsx
+++ b/data/BOLL/EXCLE/POET_1_20260826.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$17</f>
+              <f>'30日跟踪'!$A$8:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$17</f>
+              <f>'30日跟踪'!$D$8:$D$19</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -888,6 +888,46 @@
       <c r="E17" t="inlineStr">
         <is>
           <t>第10/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>7.599999904632568</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>-5.000001192092896</v>
+      </c>
+      <c r="D18" s="6">
+        <f>B18/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>第11/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>7.949999809265137</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>4.605261960848539</v>
+      </c>
+      <c r="D19" s="6">
+        <f>B19/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>第12/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/BOLL/EXCLE/POET_1_20260826.xlsx
+++ b/data/BOLL/EXCLE/POET_1_20260826.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$19</f>
+              <f>'30日跟踪'!$A$8:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$19</f>
+              <f>'30日跟踪'!$D$8:$D$20</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -928,6 +928,26 @@
       <c r="E19" t="inlineStr">
         <is>
           <t>第12/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>7.429999828338623</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>-6.540880420154127</v>
+      </c>
+      <c r="D20" s="6">
+        <f>B20/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>第13/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/BOLL/EXCLE/POET_1_20260826.xlsx
+++ b/data/BOLL/EXCLE/POET_1_20260826.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$20</f>
+              <f>'30日跟踪'!$A$8:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$20</f>
+              <f>'30日跟踪'!$D$8:$D$22</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46279</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -948,6 +948,46 @@
       <c r="E20" t="inlineStr">
         <is>
           <t>第13/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>7.210000038146973</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>-2.960966289024036</v>
+      </c>
+      <c r="D21" s="6">
+        <f>B21/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>第14/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>7.400000095367432</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>2.635229628504843</v>
+      </c>
+      <c r="D22" s="6">
+        <f>B22/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>第15/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/BOLL/EXCLE/POET_1_20260826.xlsx
+++ b/data/BOLL/EXCLE/POET_1_20260826.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$22</f>
+              <f>'30日跟踪'!$A$8:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$22</f>
+              <f>'30日跟踪'!$D$8:$D$24</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -988,6 +988,46 @@
       <c r="E22" t="inlineStr">
         <is>
           <t>第15/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>7.510000228881836</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>1.48648827157809</v>
+      </c>
+      <c r="D23" s="6">
+        <f>B23/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>第16/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>7.800000190734863</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>3.861517350395682</v>
+      </c>
+      <c r="D24" s="6">
+        <f>B24/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>第17/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/BOLL/EXCLE/POET_1_20260826.xlsx
+++ b/data/BOLL/EXCLE/POET_1_20260826.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$24</f>
+              <f>'30日跟踪'!$A$8:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$24</f>
+              <f>'30日跟踪'!$D$8:$D$25</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -1028,6 +1028,26 @@
       <c r="E24" t="inlineStr">
         <is>
           <t>第17/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>8.409999847412109</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>7.820508227702705</v>
+      </c>
+      <c r="D25" s="6">
+        <f>B25/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>第18/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/BOLL/EXCLE/POET_1_20260826.xlsx
+++ b/data/BOLL/EXCLE/POET_1_20260826.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$25</f>
+              <f>'30日跟踪'!$A$8:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$25</f>
+              <f>'30日跟踪'!$D$8:$D$26</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -1048,6 +1048,26 @@
       <c r="E25" t="inlineStr">
         <is>
           <t>第18/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>8.170000076293945</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>-2.853742871256004</v>
+      </c>
+      <c r="D26" s="6">
+        <f>B26/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>第19/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/BOLL/EXCLE/POET_1_20260826.xlsx
+++ b/data/BOLL/EXCLE/POET_1_20260826.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$26</f>
+              <f>'30日跟踪'!$A$8:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$26</f>
+              <f>'30日跟踪'!$D$8:$D$28</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46287</v>
+        <v>46289</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -1068,6 +1068,46 @@
       <c r="E26" t="inlineStr">
         <is>
           <t>第19/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>7.800000190734863</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>-4.528762326853252</v>
+      </c>
+      <c r="D27" s="6">
+        <f>B27/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>第20/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>-0.6410280706692251</v>
+      </c>
+      <c r="D28" s="6">
+        <f>B28/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>第21/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/BOLL/EXCLE/POET_1_20260826.xlsx
+++ b/data/BOLL/EXCLE/POET_1_20260826.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$28</f>
+              <f>'30日跟踪'!$A$8:$A$29</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$28</f>
+              <f>'30日跟踪'!$D$8:$D$29</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -1108,6 +1108,26 @@
       <c r="E28" t="inlineStr">
         <is>
           <t>第21/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>7.769999980926514</v>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>0.2580642700195312</v>
+      </c>
+      <c r="D29" s="6">
+        <f>B29/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>第22/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/BOLL/EXCLE/POET_1_20260826.xlsx
+++ b/data/BOLL/EXCLE/POET_1_20260826.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$29</f>
+              <f>'30日跟踪'!$A$8:$A$30</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$29</f>
+              <f>'30日跟踪'!$D$8:$D$30</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -1128,6 +1128,26 @@
       <c r="E29" t="inlineStr">
         <is>
           <t>第22/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>7.409999847412109</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>-4.633206362910148</v>
+      </c>
+      <c r="D30" s="6">
+        <f>B30/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>第23/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/BOLL/EXCLE/POET_1_20260826.xlsx
+++ b/data/BOLL/EXCLE/POET_1_20260826.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$30</f>
+              <f>'30日跟踪'!$A$8:$A$31</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$30</f>
+              <f>'30日跟踪'!$D$8:$D$31</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -1148,6 +1148,26 @@
       <c r="E30" t="inlineStr">
         <is>
           <t>第23/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>7.670000076293945</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>3.508775090901506</v>
+      </c>
+      <c r="D31" s="6">
+        <f>B31/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>第24/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/BOLL/EXCLE/POET_1_20260826.xlsx
+++ b/data/BOLL/EXCLE/POET_1_20260826.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$31</f>
+              <f>'30日跟踪'!$A$8:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$31</f>
+              <f>'30日跟踪'!$D$8:$D$32</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -1168,6 +1168,26 @@
       <c r="E31" t="inlineStr">
         <is>
           <t>第24/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>7.480000019073486</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>-2.477184554504785</v>
+      </c>
+      <c r="D32" s="6">
+        <f>B32/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>第25/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/BOLL/EXCLE/POET_1_20260826.xlsx
+++ b/data/BOLL/EXCLE/POET_1_20260826.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$32</f>
+              <f>'30日跟踪'!$A$8:$A$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$32</f>
+              <f>'30日跟踪'!$D$8:$D$33</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -1188,6 +1188,26 @@
       <c r="E32" t="inlineStr">
         <is>
           <t>第25/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>7.639999866485596</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>2.139035387755617</v>
+      </c>
+      <c r="D33" s="6">
+        <f>B33/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>第26/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/BOLL/EXCLE/POET_1_20260826.xlsx
+++ b/data/BOLL/EXCLE/POET_1_20260826.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$33</f>
+              <f>'30日跟踪'!$A$8:$A$34</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$33</f>
+              <f>'30日跟踪'!$D$8:$D$34</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -1208,6 +1208,26 @@
       <c r="E33" t="inlineStr">
         <is>
           <t>第26/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>7.789999961853027</v>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>1.963352067916091</v>
+      </c>
+      <c r="D34" s="6">
+        <f>B34/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>第27/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/BOLL/EXCLE/POET_1_20260826.xlsx
+++ b/data/BOLL/EXCLE/POET_1_20260826.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$34</f>
+              <f>'30日跟踪'!$A$8:$A$35</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$34</f>
+              <f>'30日跟踪'!$D$8:$D$35</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46297</v>
+        <v>46300</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>28/30</t>
         </is>
       </c>
     </row>
@@ -1228,6 +1228,26 @@
       <c r="E34" t="inlineStr">
         <is>
           <t>第27/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B35" s="4" t="n">
+        <v>7.809999942779541</v>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>0.256739165910802</v>
+      </c>
+      <c r="D35" s="6">
+        <f>B35/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>第28/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/BOLL/EXCLE/POET_1_20260826.xlsx
+++ b/data/BOLL/EXCLE/POET_1_20260826.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$35</f>
+              <f>'30日跟踪'!$A$8:$A$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$35</f>
+              <f>'30日跟踪'!$D$8:$D$36</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>28/30</t>
+          <t>29/30</t>
         </is>
       </c>
     </row>
@@ -1248,6 +1248,26 @@
       <c r="E35" t="inlineStr">
         <is>
           <t>第28/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B36" s="4" t="n">
+        <v>7.710000038146973</v>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>-1.280408519401077</v>
+      </c>
+      <c r="D36" s="6">
+        <f>B36/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>第29/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/BOLL/EXCLE/POET_1_20260826.xlsx
+++ b/data/BOLL/EXCLE/POET_1_20260826.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$36</f>
+              <f>'30日跟踪'!$A$8:$A$37</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$36</f>
+              <f>'30日跟踪'!$D$8:$D$37</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>29/30</t>
+          <t>30/30</t>
         </is>
       </c>
     </row>
@@ -1268,6 +1268,26 @@
       <c r="E36" t="inlineStr">
         <is>
           <t>第29/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B37" s="4" t="n">
+        <v>7.420000076293945</v>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>-3.761348384152874</v>
+      </c>
+      <c r="D37" s="6">
+        <f>B37/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>第30/30个交易日</t>
         </is>
       </c>
     </row>
